--- a/data/trans_orig/Q5401-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5401-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2007</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15999</t>
+          <t>16738</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21378</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>14190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>32974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15115</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31363</t>
+          <t>31129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41100</t>
+          <t>41649</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40814</t>
+          <t>39775</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68061</t>
+          <t>65923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73368</t>
+          <t>73254</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>91829</t>
+          <t>91320</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94951</t>
+          <t>94332</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117353</t>
+          <t>116945</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>173645</t>
+          <t>173690</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>202743</t>
+          <t>203980</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12737</t>
+          <t>13332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31358</t>
+          <t>31327</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>19833</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38921</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38525</t>
+          <t>38296</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63812</t>
+          <t>64561</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>62942</t>
+          <t>64294</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>94052</t>
+          <t>95285</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96094</t>
+          <t>95201</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116885</t>
+          <t>117159</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107350</t>
+          <t>106872</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135067</t>
+          <t>134868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>212594</t>
+          <t>210525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>246220</t>
+          <t>244579</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13230</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16472</t>
+          <t>17543</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24397</t>
+          <t>23034</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21063</t>
+          <t>21988</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40374</t>
+          <t>40943</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33529</t>
+          <t>34539</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59115</t>
+          <t>59651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76184</t>
+          <t>77174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92888</t>
+          <t>93629</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87595</t>
+          <t>88187</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108267</t>
+          <t>107962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>170660</t>
+          <t>171104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>198695</t>
+          <t>197214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,1%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>12665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>12722</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29308</t>
+          <t>29254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>18134</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>37137</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25895</t>
+          <t>26820</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35918</t>
+          <t>36153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60385</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50792</t>
+          <t>52648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>80019</t>
+          <t>81242</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103596</t>
+          <t>103564</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120734</t>
+          <t>120655</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>128283</t>
+          <t>129736</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>154635</t>
+          <t>155534</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>239303</t>
+          <t>237697</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>270760</t>
+          <t>270632</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21128</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41786</t>
+          <t>41790</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64478</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64740</t>
+          <t>62026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97913</t>
+          <t>97972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69664</t>
+          <t>69581</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>101492</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135020</t>
+          <t>136953</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>179946</t>
+          <t>182362</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>213871</t>
+          <t>214501</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>269161</t>
+          <t>269046</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>370725</t>
+          <t>369604</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>405765</t>
+          <t>404284</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>444617</t>
+          <t>442243</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>494833</t>
+          <t>492768</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>827939</t>
+          <t>826571</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>888554</t>
+          <t>889077</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,39%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2012</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>13206</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31173</t>
+          <t>31243</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18793</t>
+          <t>18622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41117</t>
+          <t>38562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36036</t>
+          <t>35057</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21093</t>
+          <t>21061</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41604</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41964</t>
+          <t>41367</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68805</t>
+          <t>69127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96686</t>
+          <t>98355</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116926</t>
+          <t>118416</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>102929</t>
+          <t>103546</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>127061</t>
+          <t>125823</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>207685</t>
+          <t>208072</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>239455</t>
+          <t>238367</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,81%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>27426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>21470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42312</t>
+          <t>42047</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36039</t>
+          <t>36954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63436</t>
+          <t>62884</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38380</t>
+          <t>38659</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36262</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60341</t>
+          <t>61103</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>59821</t>
+          <t>59214</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>92723</t>
+          <t>90674</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98101</t>
+          <t>98619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123206</t>
+          <t>122089</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99604</t>
+          <t>97965</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125950</t>
+          <t>127525</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202009</t>
+          <t>203639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>241912</t>
+          <t>240929</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,57%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22746</t>
+          <t>22235</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35703</t>
+          <t>37117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26870</t>
+          <t>27722</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52539</t>
+          <t>52450</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24334</t>
+          <t>23948</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>13919</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31792</t>
+          <t>31843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>24890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50375</t>
+          <t>50121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64411</t>
+          <t>65042</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85828</t>
+          <t>85055</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81725</t>
+          <t>81691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104427</t>
+          <t>104865</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152352</t>
+          <t>152562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183293</t>
+          <t>185229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>75,72%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27956</t>
+          <t>28324</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10761</t>
+          <t>10564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27870</t>
+          <t>28544</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25421</t>
+          <t>24932</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49297</t>
+          <t>49120</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28902</t>
+          <t>28531</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40912</t>
+          <t>39817</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68523</t>
+          <t>66427</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55590</t>
+          <t>56788</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87628</t>
+          <t>88217</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>113060</t>
+          <t>113433</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135688</t>
+          <t>136416</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>157913</t>
+          <t>158423</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>186688</t>
+          <t>187240</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>276728</t>
+          <t>278203</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>314652</t>
+          <t>314144</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41889</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71087</t>
+          <t>70021</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78318</t>
+          <t>79103</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115137</t>
+          <t>116736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>128797</t>
+          <t>126783</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>177327</t>
+          <t>178036</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>67618</t>
+          <t>66302</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104614</t>
+          <t>102908</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>131285</t>
+          <t>131518</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>176661</t>
+          <t>176386</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>208971</t>
+          <t>209938</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>268962</t>
+          <t>263875</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>397971</t>
+          <t>398943</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>441934</t>
+          <t>442326</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>468934</t>
+          <t>464219</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>519171</t>
+          <t>518613</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>882383</t>
+          <t>884710</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>949835</t>
+          <t>953322</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2016</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24776</t>
+          <t>25041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24922</t>
+          <t>25126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21259</t>
+          <t>21672</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45731</t>
+          <t>42966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6512</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18691</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24190</t>
+          <t>23826</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47427</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>33850</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59533</t>
+          <t>59013</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99206</t>
+          <t>100032</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117097</t>
+          <t>117159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>111833</t>
+          <t>111633</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136699</t>
+          <t>136527</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>216314</t>
+          <t>217499</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>248720</t>
+          <t>248152</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,02%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>19945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20439</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14562</t>
+          <t>13568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33437</t>
+          <t>32598</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17341</t>
+          <t>17675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34743</t>
+          <t>35428</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45485</t>
+          <t>44250</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74846</t>
+          <t>73565</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66630</t>
+          <t>67656</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>100147</t>
+          <t>103129</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116987</t>
+          <t>116197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137203</t>
+          <t>137285</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>133794</t>
+          <t>134564</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165870</t>
+          <t>165701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>262218</t>
+          <t>258706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>299194</t>
+          <t>295825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4116</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>20102</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>12127</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30980</t>
+          <t>30212</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41186</t>
+          <t>43439</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31266</t>
+          <t>30991</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55149</t>
+          <t>55745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85409</t>
+          <t>84009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101408</t>
+          <t>101584</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89852</t>
+          <t>88682</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112545</t>
+          <t>112699</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180911</t>
+          <t>180338</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>208838</t>
+          <t>209568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,34%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>23222</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>34145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26695</t>
+          <t>27844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45998</t>
+          <t>46755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78110</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63980</t>
+          <t>64613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99629</t>
+          <t>97904</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>138503</t>
+          <t>137716</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156271</t>
+          <t>156024</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>148567</t>
+          <t>150182</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182406</t>
+          <t>182432</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>294184</t>
+          <t>293018</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>332549</t>
+          <t>331190</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,35%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35456</t>
+          <t>34856</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58937</t>
+          <t>59064</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35517</t>
+          <t>36563</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65759</t>
+          <t>68298</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77837</t>
+          <t>78253</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>116947</t>
+          <t>117884</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54976</t>
+          <t>52557</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83648</t>
+          <t>81906</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>159745</t>
+          <t>158314</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>207988</t>
+          <t>211570</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>222810</t>
+          <t>223373</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>283250</t>
+          <t>282504</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>461198</t>
+          <t>460230</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>495858</t>
+          <t>496806</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>516162</t>
+          <t>515861</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>572672</t>
+          <t>569273</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>982338</t>
+          <t>989697</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1053260</t>
+          <t>1052949</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,9%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si son capaces de realizar las tareas de la casa en 2023</t>
+          <t>Población según si son capaces de realizar las tareas de la casa en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23246</t>
+          <t>23590</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21143</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32672</t>
+          <t>33271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35834</t>
+          <t>36462</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52380</t>
+          <t>52727</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22219</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>37224</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34098</t>
+          <t>33534</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48026</t>
+          <t>48059</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58423</t>
+          <t>59810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79960</t>
+          <t>81327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93507</t>
+          <t>93147</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111317</t>
+          <t>112051</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>103749</t>
+          <t>102853</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>119737</t>
+          <t>119869</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>202020</t>
+          <t>201490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>226433</t>
+          <t>225495</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16402</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20702</t>
+          <t>20534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35123</t>
+          <t>34475</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30729</t>
+          <t>30144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48147</t>
+          <t>46576</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>42671</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59354</t>
+          <t>60545</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>62062</t>
+          <t>61786</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>84734</t>
+          <t>83744</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118139</t>
+          <t>117841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134546</t>
+          <t>133690</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130129</t>
+          <t>130465</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150596</t>
+          <t>149567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>253436</t>
+          <t>254238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>278783</t>
+          <t>279176</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,69%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11814</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42350</t>
+          <t>40726</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40769</t>
+          <t>40907</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16039</t>
+          <t>16709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86337</t>
+          <t>83338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79736</t>
+          <t>80286</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113077</t>
+          <t>112830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126205</t>
+          <t>125846</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>235180</t>
+          <t>239399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>347578</t>
+          <t>346086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>377870</t>
+          <t>378517</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>478754</t>
+          <t>474428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8772</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>21266</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>22177</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37465</t>
+          <t>37770</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35054</t>
+          <t>34587</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54557</t>
+          <t>54145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33293</t>
+          <t>32518</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50699</t>
+          <t>50151</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70212</t>
+          <t>69685</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72816</t>
+          <t>70815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98187</t>
+          <t>96848</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155096</t>
+          <t>155740</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>173237</t>
+          <t>173234</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>174049</t>
+          <t>173363</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>196834</t>
+          <t>197090</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>335687</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>364319</t>
+          <t>365201</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,28%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39498</t>
+          <t>39042</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59146</t>
+          <t>60578</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53533</t>
+          <t>49995</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128064</t>
+          <t>128406</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>95021</t>
+          <t>96701</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>175068</t>
+          <t>175081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73485</t>
+          <t>72942</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100588</t>
+          <t>99479</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>103087</t>
+          <t>93536</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>239566</t>
+          <t>238004</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>169144</t>
+          <t>178193</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>318879</t>
+          <t>318079</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>497829</t>
+          <t>497166</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>529399</t>
+          <t>529344</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>669504</t>
+          <t>671621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>877374</t>
+          <t>885311</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1194324</t>
+          <t>1197340</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1418749</t>
+          <t>1409590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5401-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5401-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16738</t>
+          <t>15939</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20993</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>14951</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32974</t>
+          <t>34148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31129</t>
+          <t>31388</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21721</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41649</t>
+          <t>41495</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39775</t>
+          <t>40890</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65923</t>
+          <t>66881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73254</t>
+          <t>73157</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>91320</t>
+          <t>92173</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94332</t>
+          <t>94935</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>116945</t>
+          <t>117299</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>173690</t>
+          <t>173112</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>203980</t>
+          <t>203097</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19627</t>
+          <t>18770</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>13495</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31327</t>
+          <t>32523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19833</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38921</t>
+          <t>38890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38296</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64561</t>
+          <t>61815</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>64294</t>
+          <t>64435</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95285</t>
+          <t>95344</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95201</t>
+          <t>95029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117159</t>
+          <t>116763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106872</t>
+          <t>109536</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134868</t>
+          <t>134705</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>210525</t>
+          <t>210228</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>244579</t>
+          <t>244307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,35%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2534</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17543</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23034</t>
+          <t>24528</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21988</t>
+          <t>22087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40943</t>
+          <t>42127</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34539</t>
+          <t>34003</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59651</t>
+          <t>59382</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77174</t>
+          <t>77442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93629</t>
+          <t>93264</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88187</t>
+          <t>86748</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107962</t>
+          <t>107897</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171104</t>
+          <t>170721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>197214</t>
+          <t>197477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,21%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>12720</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29254</t>
+          <t>29127</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18134</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37137</t>
+          <t>36464</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>26572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36153</t>
+          <t>34737</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59243</t>
+          <t>58207</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52648</t>
+          <t>52045</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81242</t>
+          <t>81002</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>103564</t>
+          <t>103551</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120655</t>
+          <t>120771</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>129736</t>
+          <t>129349</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>155534</t>
+          <t>156008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>237697</t>
+          <t>237848</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>270632</t>
+          <t>270643</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41790</t>
+          <t>41149</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35704</t>
+          <t>37059</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64637</t>
+          <t>65040</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>62026</t>
+          <t>62533</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>97972</t>
+          <t>96481</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69581</t>
+          <t>69075</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>101492</t>
+          <t>103252</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>136953</t>
+          <t>136621</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>182362</t>
+          <t>180706</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>214501</t>
+          <t>216785</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>269046</t>
+          <t>270684</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>369604</t>
+          <t>367864</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>404284</t>
+          <t>405105</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>442243</t>
+          <t>444283</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>492768</t>
+          <t>493120</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>826571</t>
+          <t>829621</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>889077</t>
+          <t>888570</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,35%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2219</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31243</t>
+          <t>31364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18622</t>
+          <t>19062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38562</t>
+          <t>40164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35057</t>
+          <t>35790</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21061</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>41307</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41367</t>
+          <t>41268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69127</t>
+          <t>69205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98355</t>
+          <t>96955</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118416</t>
+          <t>117628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>103546</t>
+          <t>103904</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>125823</t>
+          <t>126856</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>208072</t>
+          <t>208336</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>238367</t>
+          <t>240587</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>78,54%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>10446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27426</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21470</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42047</t>
+          <t>41475</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36954</t>
+          <t>36829</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62884</t>
+          <t>61843</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38659</t>
+          <t>38042</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61103</t>
+          <t>60426</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>59214</t>
+          <t>61470</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>90674</t>
+          <t>91172</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98619</t>
+          <t>98867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122089</t>
+          <t>122856</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97965</t>
+          <t>99817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127525</t>
+          <t>125268</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203639</t>
+          <t>205364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>240929</t>
+          <t>240566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22235</t>
+          <t>22875</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37117</t>
+          <t>35966</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27722</t>
+          <t>27750</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52450</t>
+          <t>51269</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>24454</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13919</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24890</t>
+          <t>25797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50121</t>
+          <t>50365</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65042</t>
+          <t>64542</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85055</t>
+          <t>84971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81691</t>
+          <t>81974</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104865</t>
+          <t>105844</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152562</t>
+          <t>154710</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>185229</t>
+          <t>185532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,85%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28324</t>
+          <t>27998</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28544</t>
+          <t>27871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24932</t>
+          <t>25055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49120</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28531</t>
+          <t>27959</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39817</t>
+          <t>41315</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66427</t>
+          <t>68460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56788</t>
+          <t>57854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88217</t>
+          <t>89492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>113433</t>
+          <t>112274</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136416</t>
+          <t>135248</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158423</t>
+          <t>157091</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>187240</t>
+          <t>185674</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>278203</t>
+          <t>278616</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>314144</t>
+          <t>314801</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70021</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>79103</t>
+          <t>77879</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>116736</t>
+          <t>114552</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126783</t>
+          <t>128282</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>176251</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66302</t>
+          <t>66315</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>102908</t>
+          <t>104273</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>131518</t>
+          <t>132960</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>176386</t>
+          <t>177987</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>209938</t>
+          <t>207890</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>263875</t>
+          <t>265733</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>398943</t>
+          <t>397822</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>442326</t>
+          <t>443466</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>464219</t>
+          <t>467327</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>518613</t>
+          <t>518344</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>884710</t>
+          <t>881057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>953322</t>
+          <t>948505</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25041</t>
+          <t>24744</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25126</t>
+          <t>24027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21672</t>
+          <t>21418</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42966</t>
+          <t>43630</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>18142</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23826</t>
+          <t>23667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>44041</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33850</t>
+          <t>33977</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59013</t>
+          <t>60268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100032</t>
+          <t>99912</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117159</t>
+          <t>117833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>111633</t>
+          <t>112067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136527</t>
+          <t>137128</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>217499</t>
+          <t>216777</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>248152</t>
+          <t>248464</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19945</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19020</t>
+          <t>19272</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>13426</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32598</t>
+          <t>32778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35428</t>
+          <t>35910</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44250</t>
+          <t>43409</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73565</t>
+          <t>72176</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>67656</t>
+          <t>67127</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>103129</t>
+          <t>101417</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116197</t>
+          <t>116447</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137285</t>
+          <t>136274</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134564</t>
+          <t>136572</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165701</t>
+          <t>166812</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>258706</t>
+          <t>258665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>295825</t>
+          <t>297156</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15960</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20102</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12127</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>31171</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20359</t>
+          <t>20290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>41026</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30991</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>55874</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84009</t>
+          <t>84877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101584</t>
+          <t>101422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88682</t>
+          <t>89197</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112699</t>
+          <t>113322</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180338</t>
+          <t>180409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209568</t>
+          <t>209077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,15%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23222</t>
+          <t>24029</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>14881</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34145</t>
+          <t>35541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>12088</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27844</t>
+          <t>28965</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46755</t>
+          <t>47008</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>77299</t>
+          <t>77052</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64613</t>
+          <t>63917</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>97904</t>
+          <t>97949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>137716</t>
+          <t>136643</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>156024</t>
+          <t>155731</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>150182</t>
+          <t>150989</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182432</t>
+          <t>183126</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>293018</t>
+          <t>293647</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>331190</t>
+          <t>331876</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34856</t>
+          <t>34604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59064</t>
+          <t>58111</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>34955</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68298</t>
+          <t>66474</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78253</t>
+          <t>77294</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>117884</t>
+          <t>115569</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52557</t>
+          <t>54213</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>81906</t>
+          <t>82250</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>158314</t>
+          <t>158633</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>211570</t>
+          <t>211814</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>223373</t>
+          <t>219475</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>282504</t>
+          <t>279484</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>460230</t>
+          <t>460615</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>496806</t>
+          <t>496080</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>515861</t>
+          <t>515447</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>569273</t>
+          <t>573374</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>989697</t>
+          <t>991180</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1052949</t>
+          <t>1055888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16608</t>
+          <t>17452</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11669</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23590</t>
+          <t>25006</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26850</t>
+          <t>28257</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21155</t>
+          <t>22467</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33271</t>
+          <t>35415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>45709</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36462</t>
+          <t>37481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52727</t>
+          <t>55333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28690</t>
+          <t>30666</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21956</t>
+          <t>23300</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37224</t>
+          <t>39439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40780</t>
+          <t>43847</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33534</t>
+          <t>36486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48059</t>
+          <t>53455</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>69470</t>
+          <t>74513</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59810</t>
+          <t>64334</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81327</t>
+          <t>86080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>102785</t>
+          <t>115197</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93147</t>
+          <t>105437</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112051</t>
+          <t>123861</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,17 +8525,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>111533</t>
+          <t>118925</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>102853</t>
+          <t>109482</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>119869</t>
+          <t>127638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>214317</t>
+          <t>234121</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>221441</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>225495</t>
+          <t>246767</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,64%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>17490</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>27035</t>
+          <t>29144</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20534</t>
+          <t>22654</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>37494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>38557</t>
+          <t>41132</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30144</t>
+          <t>32886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46576</t>
+          <t>50558</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22065</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15682</t>
+          <t>17332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50966</t>
+          <t>56514</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42671</t>
+          <t>47630</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60545</t>
+          <t>67083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>73031</t>
+          <t>80884</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>61786</t>
+          <t>68433</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>83744</t>
+          <t>93218</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>126527</t>
+          <t>141845</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117841</t>
+          <t>132660</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>133690</t>
+          <t>150381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>140745</t>
+          <t>156382</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130465</t>
+          <t>144612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149567</t>
+          <t>167321</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>267272</t>
+          <t>298226</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>254238</t>
+          <t>284307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>279176</t>
+          <t>312405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>13490</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>17866</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40726</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>25110</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>17355</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40907</t>
+          <t>33923</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16709</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34424</t>
+          <t>38284</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83338</t>
+          <t>48096</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>44747</t>
+          <t>50762</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13817</t>
+          <t>40939</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80286</t>
+          <t>61947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>120410</t>
+          <t>140064</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112830</t>
+          <t>131075</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125846</t>
+          <t>146338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>309818</t>
+          <t>118758</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>239399</t>
+          <t>108820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>346086</t>
+          <t>127945</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>430229</t>
+          <t>258822</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378517</t>
+          <t>245327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>474428</t>
+          <t>270603</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14497</t>
+          <t>14742</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>21014</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29126</t>
+          <t>32361</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22177</t>
+          <t>25317</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37770</t>
+          <t>42078</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>43624</t>
+          <t>47103</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34587</t>
+          <t>37782</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54145</t>
+          <t>58162</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>25319</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32518</t>
+          <t>32966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>59727</t>
+          <t>64693</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50151</t>
+          <t>54667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69685</t>
+          <t>76833</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>84151</t>
+          <t>90012</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70815</t>
+          <t>76650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>96848</t>
+          <t>103756</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>173563</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155740</t>
+          <t>164122</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>173234</t>
+          <t>182492</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>186204</t>
+          <t>197743</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>173363</t>
+          <t>183421</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>197090</t>
+          <t>208874</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>350993</t>
+          <t>371307</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>336521</t>
+          <t>355714</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>365201</t>
+          <t>386978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>203709</t>
+          <t>213625</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>203709</t>
+          <t>213625</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>203709</t>
+          <t>213625</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>275058</t>
+          <t>294797</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275058</t>
+          <t>294797</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275058</t>
+          <t>294797</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>478767</t>
+          <t>508422</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>478767</t>
+          <t>508422</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>478767</t>
+          <t>508422</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>48847</t>
+          <t>51426</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39042</t>
+          <t>41678</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60578</t>
+          <t>62648</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>99025</t>
+          <t>107629</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49995</t>
+          <t>93031</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128406</t>
+          <t>123595</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>147872</t>
+          <t>159054</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96701</t>
+          <t>141948</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>175081</t>
+          <t>178254</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>85501</t>
+          <t>92834</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72942</t>
+          <t>78750</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>99479</t>
+          <t>107664</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>185898</t>
+          <t>203338</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93536</t>
+          <t>184564</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>238004</t>
+          <t>224710</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>271399</t>
+          <t>296171</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>178193</t>
+          <t>272527</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>318079</t>
+          <t>320248</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>514510</t>
+          <t>570669</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>497166</t>
+          <t>552732</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>529344</t>
+          <t>587790</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>748301</t>
+          <t>591809</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>671621</t>
+          <t>569667</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>885311</t>
+          <t>612395</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1262810</t>
+          <t>1162477</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1197340</t>
+          <t>1133967</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1409590</t>
+          <t>1190182</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>73,57%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>648858</t>
+          <t>714928</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>648858</t>
+          <t>714928</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648858</t>
+          <t>714928</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1033224</t>
+          <t>902775</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1033224</t>
+          <t>902775</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1033224</t>
+          <t>902775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1682081</t>
+          <t>1617703</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1682081</t>
+          <t>1617703</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1682081</t>
+          <t>1617703</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
